--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS6801R_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS6801R_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ3"/>
+  <dimension ref="A1:BJ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,110 +934,110 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FS6801-08-06-NWO-FG</t>
+          <t>FS6801-06-10-NWO-FG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.375</v>
+        <v>0.53</v>
       </c>
       <c r="D3" t="n">
-        <v>0.40625</v>
+        <v>0.34375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.45725</v>
+        <v>0.39425</v>
       </c>
       <c r="F3" t="n">
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3595</v>
+        <v>0.297</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3145</v>
+        <v>0.252</v>
       </c>
       <c r="I3" t="n">
         <v>0.052</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2125</v>
+        <v>0.15</v>
       </c>
       <c r="K3" t="n">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="L3" t="n">
-        <v>0.375</v>
+        <v>0.53</v>
       </c>
       <c r="M3" t="n">
-        <v>0.537</v>
+        <v>0.784</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3</v>
+        <v>0.4375</v>
       </c>
       <c r="O3" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="P3" t="n">
-        <v>0.38</v>
+        <v>0.535</v>
       </c>
       <c r="Q3" t="n">
         <v>75</v>
       </c>
       <c r="R3" t="n">
-        <v>0.44301</v>
+        <v>0.62199</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
       </c>
       <c r="T3" t="n">
-        <v>0.33</v>
+        <v>0.45</v>
       </c>
       <c r="U3" t="n">
-        <v>0.38</v>
+        <v>0.535</v>
       </c>
       <c r="V3" t="n">
-        <v>0.397</v>
+        <v>0.5775</v>
       </c>
       <c r="W3" t="n">
-        <v>0.035</v>
+        <v>0.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2405</v>
+        <v>0.3865</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.28125</v>
+        <v>0.4375</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.377</v>
+        <v>0.461</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.33</v>
+        <v>0.45</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3</v>
+        <v>0.49</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="AH3" t="n">
         <v>0.0625</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.45725</v>
+        <v>0.39425</v>
       </c>
       <c r="AJ3" t="n">
         <v>0.03383</v>
@@ -1049,93 +1049,1341 @@
         <v>0.0625</v>
       </c>
       <c r="AM3" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.61149</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>FS6801-06-10-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Face Seal x Adjustable Male ORB Elbow - stud neck below the flats, 11/16-16 UN (male O-ring face seal, SAE J1453) x 7/8-14 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>FS6801R</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>7/8-14 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21: THDMAJ_N@DRIVE] Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-06-10-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-6-10 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF6801-6-10 NWO = Brennan forged FS6801-06-10-NWO-FG p10 on every compared cell (M LGTH ~ L7, N LGTH ~ L10, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | Air-Way thread printing slip: n UN/UNF-2A "7/8-12" where Air-Way prints 7/8-14 for this dash - THDMAJ left empty, the thread comes from the end library by dash (plan D1) | forged (-FG): the Air-Way NON-forged series FF6801 is used only where Brennan FS6801-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5645 (no dimensions) | Brennan CAD record FS6801-06-10-NWO-FG (PARTcommunity / CADENAS, THDMAJ_N@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 2: adjustable stud tip -&gt; washer face 0.63 = L10 - L11 (Air-Way), thread 0.461 = stud - undercut 0.169, tip -&gt; body face 1.186 (FS lock nut 0.45 thick, NWO_FS)</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>FS6801-06-10-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FS6801-08-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="F4" t="n">
+        <v>45</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.44301</v>
+      </c>
+      <c r="S4" t="n">
+        <v>75</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AM4" t="n">
         <v>0.5625</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AN4" t="n">
         <v>0.05556</v>
       </c>
-      <c r="AO3" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="AP3" t="n">
+      <c r="AO4" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="AP4" t="n">
         <v>0.03007</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AQ4" t="n">
         <v>0.01389</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AR4" t="n">
         <v>0.05556</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AS4" t="n">
         <v>0.75</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AT4" t="n">
         <v>0.596</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AU4" t="n">
         <v>0.75</v>
       </c>
-      <c r="AV3" t="n">
-        <v>0.537</v>
-      </c>
-      <c r="AW3" t="n">
+      <c r="AV4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="AW4" t="n">
         <v>0.375</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AX4" t="n">
         <v>0.375</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="AY4" t="n">
         <v>0.21601</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="AZ4" t="n">
         <v>0.21601</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BA4" t="n">
         <v>0.43251</v>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>FS6801-08-06-NWO-FG</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>ORFS 90 deg Male Face Seal x Adjustable Male ORB Elbow - stud neck below the flats, 13/16-16 UN (male O-ring face seal, SAE J1453) x 9/16-18 (adjustable male ORB)</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>FS6801R</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>9/16-18 (adjustable male ORB)</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-08-06-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-8-6 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>forged (-FG): Air-Way non-forged FF6801-8-6 NWO = Brennan forged FS6801-08-06-NWO-FG p10 on every compared cell (M LGTH ~ L7, N LGTH ~ L10, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6801 is used only where Brennan FS6801-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5647 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 2: adjustable stud tip -&gt; washer face 0.48 = L10 - L11 (Air-Way), thread 0.377 = stud - undercut 0.103, tip -&gt; body face 0.903 (FS lock nut 0.33 thick, NWO_FS)</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF6801-8-6 NWO = Brennan forged FS6801-08-06-NWO-FG p10 on every compared cell (M LGTH ~ L7, N LGTH ~ L10, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6801 is used only where Brennan FS6801-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5647 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 2: adjustable stud tip -&gt; washer face 0.48 = L10 - L11 (Air-Way), thread 0.359 = stud - undercut 0.121, tip -&gt; body face 0.885 (FS lock nut 0.33 thick, NWO_FS)</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>FS6801-08-06-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FS6801-08-12-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="F5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5312</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>75</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.80674</v>
+      </c>
+      <c r="S5" t="n">
+        <v>75</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.68655</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>FS6801-08-12-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Face Seal x Adjustable Male ORB Elbow - stud neck below the flats, 13/16-16 UN (male O-ring face seal, SAE J1453) x 1 1/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>FS6801R</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-08-12-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-8-12 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF6801-8-12 NWO = Brennan forged FS6801-08-12-NWO-FG p10 on every compared cell (M LGTH ~ L7, N LGTH ~ L10, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6801 is used only where Brennan FS6801-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5650 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 2: adjustable stud tip -&gt; washer face 0.73 = L10 - L11 (Air-Way), thread 0.546 = stud - undercut 0.184, tip -&gt; body face 1.333 (FS lock nut 0.5 thick, NWO_FS)</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>FS6801-08-12-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FS6801-10-10-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="F6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.62199</v>
+      </c>
+      <c r="S6" t="n">
+        <v>75</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.5775</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.61149</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>FS6801-10-10-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Face Seal x Adjustable Male ORB Elbow - stud neck below the flats, 1-14 UN (male O-ring face seal, SAE J1453) x 7/8-14 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>FS6801R</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>1-14 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>7/8-14 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-10-10-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-10-10 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF6801-10-10 NWO = Brennan forged FS6801-10-10-NWO-FG p10 on every compared cell (M LGTH ~ L7, N LGTH ~ L10, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6801 is used only where Brennan FS6801-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5652 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 2: adjustable stud tip -&gt; washer face 0.63 = L10 - L11 (Air-Way), thread 0.461 = stud - undercut 0.169, tip -&gt; body face 1.186 (FS lock nut 0.45 thick, NWO_FS)</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>FS6801-10-10-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FS6801-10-12-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="F7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5312</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.6925</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.80386</v>
+      </c>
+      <c r="S7" t="n">
+        <v>75</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.6925</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.6853900000000001</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>FS6801-10-12-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Face Seal x Adjustable Male ORB Elbow - stud neck below the flats, 1-14 UN (male O-ring face seal, SAE J1453) x 1 1/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>FS6801R</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>1-14 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7@DRIVE: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "M LGTH" = "1.410" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 619.2, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 20/20 rows with an Air-Way value agree to rounding; L10@DRIVE: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "N LGTH" = "2.170" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 619.2, page verified True) [Brennan = yes 2026-10-18] - adjustable stud tip -&gt; crossing; mapping: same-table check: 20/20 rows with an Air-Way value agree to rounding; S3HEX@HEX: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "C HEX" = "1.375" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 619.2, page verified True) [Brennan = yes 2026-10-18] - lock nut hex; mapping: same-table check: 20/20 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "JJ FLATS" = "1.188" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 619.2, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 20/20 rows with an Air-Way value agree to rounding; THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -10 = 1.0 (PLAN.md s2 FS_THR / the -10 thread of every staged ORFS row); = Brennan "A THREAD" "1-14" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_N@DRIVE: end library: straight (UN/UNF) thread of dash -12 = 1.0625 (PLAN.md s2 FS_THR / the -12 thread of every staged ORFS row); = Brennan "B THREAD" "1-1/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "A THREAD" "1-14" in the table's format; $PRP@Thread_N: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "B THREAD" "1-1/16-12" in the table's format; L11@DRIVE: approved derived (user 2026-10-18 Q-FS-XFER yes): L10@DRIVE 2.17 (Brennan) - Air-Way stud length 0.73 of ORB -12 (L10@DRIVE - L11@DRIVE on every Air-Way row of FS6801 with this ORB dash; Q-FS-ORBSTUD (a) end ORB_FS / NWO_FS); D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6801: FSM -10 bore on 4 Air-Way row(s): 0.49 (unanimous) [Air-Way, not Brennan]; D20@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6801: ORB -12 bore on 4 Air-Way row(s): 0.61 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on JJ FLATS=1.188 vs Air-Way S2=1.06 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF6801 is used only where Brennan FS6801-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5653 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p10 FS6801-10-12-NWO-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library) | leg 2: adjustable stud tip -&gt; washer face 0.73 = L10 - L11 (Air-Way), thread 0.546 = stud - undercut 0.184, tip -&gt; body face 1.333 (FS lock nut 0.5 thick, NWO_FS)</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>FS6801-10-12-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FS6801-12-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.60775</v>
+      </c>
+      <c r="F8" t="n">
+        <v>45</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5315</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.6562</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.95108</v>
+      </c>
+      <c r="S8" t="n">
+        <v>75</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.5975</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.60775</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.41519</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.41519</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.83088</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>FS6801-12-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Face Seal x Adjustable Male ORB Elbow - stud neck below the flats, 1 3/16-12 UN (male O-ring face seal, SAE J1453) x 1 5/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>FS6801R</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>1 3/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-12-16-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-12-16 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF6801-12-16 NWO = Brennan forged FS6801-12-16-NWO-FG p10 on every compared cell (M LGTH ~ L7, N LGTH ~ L10, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6801 is used only where Brennan FS6801-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5657 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 2: adjustable stud tip -&gt; washer face 0.73 = L10 - L11 (Air-Way), thread 0.546 = stud - undercut 0.184, tip -&gt; body face 1.363 (FS lock nut 0.54 thick, NWO_FS)</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>FS6801-12-16-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FS6801-20-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.62775</v>
+      </c>
+      <c r="F9" t="n">
+        <v>45</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7825</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6562</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>75</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.95108</v>
+      </c>
+      <c r="S9" t="n">
+        <v>75</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.5975</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.62775</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.94058</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>FS6801-20-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Face Seal x Adjustable Male ORB Elbow - stud neck below the flats, 1 11/16-12 UN (male O-ring face seal, SAE J1453) x 1 5/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>FS6801R</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>1 11/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-20-16-NWO-FG (ORFS-p010-t03); FORGED part: Air-Way NON-forged row FF6801-20-16 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF6801-20-16 NWO = Brennan forged FS6801-20-16-NWO-FG p10 on every compared cell (M LGTH ~ L7, N LGTH ~ L10, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6801 is used only where Brennan FS6801-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5661 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 2: adjustable stud tip -&gt; washer face 0.73 = L10 - L11 (Air-Way), thread 0.546 = stud - undercut 0.184, tip -&gt; body face 1.363 (FS lock nut 0.54 thick, NWO_FS)</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>FS6801-20-16-NWO-FG</t>
         </is>
       </c>
     </row>

--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS6801R_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS6801R_SW2.xlsx
@@ -917,7 +917,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-10-08-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-10-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-10-08-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-10-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: THDMAJ_N@DRIVE] Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-06-10-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-6-10 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-CAD 2026-10-21: THDMAJ_N@DRIVE] Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-06-10-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-6-10 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-08-06-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-8-6 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-08-06-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-8-6 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-08-12-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-8-12 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-08-12-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-8-12 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-10-10-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-10-10 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-10-10-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-10-10 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7@DRIVE: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "M LGTH" = "1.410" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 619.2, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 20/20 rows with an Air-Way value agree to rounding; L10@DRIVE: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "N LGTH" = "2.170" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 619.2, page verified True) [Brennan = yes 2026-10-18] - adjustable stud tip -&gt; crossing; mapping: same-table check: 20/20 rows with an Air-Way value agree to rounding; S3HEX@HEX: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "C HEX" = "1.375" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 619.2, page verified True) [Brennan = yes 2026-10-18] - lock nut hex; mapping: same-table check: 20/20 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "JJ FLATS" = "1.188" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 619.2, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 20/20 rows with an Air-Way value agree to rounding; THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -10 = 1.0 (PLAN.md s2 FS_THR / the -10 thread of every staged ORFS row); = Brennan "A THREAD" "1-14" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_N@DRIVE: end library: straight (UN/UNF) thread of dash -12 = 1.0625 (PLAN.md s2 FS_THR / the -12 thread of every staged ORFS row); = Brennan "B THREAD" "1-1/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "A THREAD" "1-14" in the table's format; $PRP@Thread_N: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "B THREAD" "1-1/16-12" in the table's format; L11@DRIVE: approved derived (user 2026-10-18 Q-FS-XFER yes): L10@DRIVE 2.17 (Brennan) - Air-Way stud length 0.73 of ORB -12 (L10@DRIVE - L11@DRIVE on every Air-Way row of FS6801 with this ORB dash; Q-FS-ORBSTUD (a) end ORB_FS / NWO_FS); D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6801: FSM -10 bore on 4 Air-Way row(s): 0.49 (unanimous) [Air-Way, not Brennan]; D20@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6801: ORB -12 bore on 4 Air-Way row(s): 0.61 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7@DRIVE: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "M LGTH" = "1.410" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 619.2, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 20/20 rows with an Air-Way value agree to rounding; L10@DRIVE: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "N LGTH" = "2.170" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 619.2, page verified True) [Brennan = yes 2026-10-18] - adjustable stud tip -&gt; crossing; mapping: same-table check: 20/20 rows with an Air-Way value agree to rounding; S3HEX@HEX: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "C HEX" = "1.375" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 619.2, page verified True) [Brennan = yes 2026-10-18] - lock nut hex; mapping: same-table check: 20/20 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "JJ FLATS" = "1.188" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 619.2, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 20/20 rows with an Air-Way value agree to rounding; THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -10 = 1.0 (PLAN.md s2 FS_THR / the -10 thread of every staged ORFS row); = Brennan "A THREAD" "1-14" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_N@DRIVE: end library: straight (UN/UNF) thread of dash -12 = 1.0625 (PLAN.md s2 FS_THR / the -12 thread of every staged ORFS row); = Brennan "B THREAD" "1-1/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "A THREAD" "1-14" in the table's format; $PRP@Thread_N: Brennan ORFS catalog p10 table ORFS-p010-t02 "FS6801-NWO-FG MFS-MAORB 90 DEG ELBOW" row FS6801-10-12-NWO-FG col "B THREAD" "1-1/16-12" in the table's format; L11@DRIVE: approved derived (user 2026-10-18 Q-FS-XFER yes): L10@DRIVE 2.17 (Brennan) - Air-Way stud length 0.73 of ORB -12 (L10@DRIVE - L11@DRIVE on every Air-Way row of FS6801 with this ORB dash; Q-FS-ORBSTUD (a) end ORB_FS / NWO_FS); D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6801: FSM -10 bore on 4 Air-Way row(s): 0.49 (unanimous) [Air-Way, not Brennan]; D20@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6801: ORB -12 bore on 4 Air-Way row(s): 0.61 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-12-16-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-12-16 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-12-16-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-12-16 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-20-16-NWO-FG (ORFS-p010-t03); FORGED part: Air-Way NON-forged row FF6801-20-16 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-20-16-NWO-FG (ORFS-p010-t03); FORGED part: Air-Way NON-forged row FF6801-20-16 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
